--- a/output/graficos_dimensiones/comunal_d_env_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:15</t>
+    <t xml:space="preserve">2026-09-10 01:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:28</t>
+    <t xml:space="preserve">2026-09-12 22:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_metropolitana.xlsx
@@ -60,24 +60,24 @@
     <t xml:space="preserve">La Reina</t>
   </si>
   <si>
+    <t xml:space="preserve">Calera de Tango</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vitacura</t>
   </si>
   <si>
-    <t xml:space="preserve">Calera de Tango</t>
-  </si>
-  <si>
     <t xml:space="preserve">La Florida</t>
   </si>
   <si>
     <t xml:space="preserve">Lo Prado</t>
   </si>
   <si>
+    <t xml:space="preserve">Conchalí</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quinta Normal</t>
   </si>
   <si>
-    <t xml:space="preserve">Conchalí</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Miguel</t>
   </si>
   <si>
@@ -96,30 +96,30 @@
     <t xml:space="preserve">María Pinto</t>
   </si>
   <si>
+    <t xml:space="preserve">La Granja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pirque</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recoleta</t>
   </si>
   <si>
-    <t xml:space="preserve">La Granja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pirque</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lo Espejo</t>
   </si>
   <si>
+    <t xml:space="preserve">Cerro Navia</t>
+  </si>
+  <si>
     <t xml:space="preserve">Santiago</t>
   </si>
   <si>
-    <t xml:space="preserve">Cerro Navia</t>
+    <t xml:space="preserve">Cerrillos</t>
   </si>
   <si>
     <t xml:space="preserve">Independencia</t>
   </si>
   <si>
-    <t xml:space="preserve">Cerrillos</t>
-  </si>
-  <si>
     <t xml:space="preserve">El Bosque</t>
   </si>
   <si>
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:40</t>
+    <t xml:space="preserve">2026-09-24 00:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -634,7 +634,7 @@
         <v>2018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>151.86</v>
+        <v>159.86</v>
       </c>
     </row>
     <row r="3">
@@ -651,7 +651,7 @@
         <v>2018</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>126.45</v>
+        <v>134.7</v>
       </c>
     </row>
     <row r="4">
@@ -668,7 +668,7 @@
         <v>2018</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>124.7</v>
+        <v>132.35</v>
       </c>
     </row>
     <row r="5">
@@ -685,7 +685,7 @@
         <v>2018</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>118.45</v>
+        <v>126.76</v>
       </c>
     </row>
     <row r="6">
@@ -702,7 +702,7 @@
         <v>2018</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>117.23</v>
+        <v>125.35</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>2018</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>113.39</v>
+        <v>121.19</v>
       </c>
     </row>
     <row r="8">
@@ -736,7 +736,7 @@
         <v>2018</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>110.39</v>
+        <v>118.35</v>
       </c>
     </row>
     <row r="9">
@@ -753,7 +753,7 @@
         <v>2018</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>109.42</v>
+        <v>117.64</v>
       </c>
     </row>
     <row r="10">
@@ -764,13 +764,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>13132</v>
+        <v>13403</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>107.78</v>
+        <v>115.08</v>
       </c>
     </row>
     <row r="11">
@@ -781,13 +781,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>13403</v>
+        <v>13132</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>107.41</v>
+        <v>114.46</v>
       </c>
     </row>
     <row r="12">
@@ -804,7 +804,7 @@
         <v>2018</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>103.17</v>
+        <v>110.52</v>
       </c>
     </row>
     <row r="13">
@@ -821,7 +821,7 @@
         <v>2018</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>102.37</v>
+        <v>109.91</v>
       </c>
     </row>
     <row r="14">
@@ -832,13 +832,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>13126</v>
+        <v>13104</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>101.65</v>
+        <v>108.68</v>
       </c>
     </row>
     <row r="15">
@@ -849,13 +849,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>13104</v>
+        <v>13126</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>101.6</v>
+        <v>108.34</v>
       </c>
     </row>
     <row r="16">
@@ -872,7 +872,7 @@
         <v>2018</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>100.77</v>
+        <v>106.63</v>
       </c>
     </row>
     <row r="17">
@@ -889,7 +889,7 @@
         <v>2018</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>99.04</v>
+        <v>106.18</v>
       </c>
     </row>
     <row r="18">
@@ -906,7 +906,7 @@
         <v>2018</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>96.25</v>
+        <v>102.53</v>
       </c>
     </row>
     <row r="19">
@@ -923,7 +923,7 @@
         <v>2018</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>95.02</v>
+        <v>102.47</v>
       </c>
     </row>
     <row r="20">
@@ -940,7 +940,7 @@
         <v>2018</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>94.22</v>
+        <v>101.23</v>
       </c>
     </row>
     <row r="21">
@@ -957,7 +957,7 @@
         <v>2018</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>93.85</v>
+        <v>100.98</v>
       </c>
     </row>
     <row r="22">
@@ -968,13 +968,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>13127</v>
+        <v>13111</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>92.78</v>
+        <v>99.27</v>
       </c>
     </row>
     <row r="23">
@@ -985,13 +985,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>13111</v>
+        <v>13202</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>92.57</v>
+        <v>98.67</v>
       </c>
     </row>
     <row r="24">
@@ -1002,13 +1002,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>13202</v>
+        <v>13127</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>92.12</v>
+        <v>98.57</v>
       </c>
     </row>
     <row r="25">
@@ -1025,7 +1025,7 @@
         <v>2018</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>90.98</v>
+        <v>97.38</v>
       </c>
     </row>
     <row r="26">
@@ -1036,13 +1036,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>13101</v>
+        <v>13103</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>90.25</v>
+        <v>96.25</v>
       </c>
     </row>
     <row r="27">
@@ -1053,13 +1053,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>13103</v>
+        <v>13101</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>89.84</v>
+        <v>95.01</v>
       </c>
     </row>
     <row r="28">
@@ -1070,13 +1070,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>13108</v>
+        <v>13102</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>87.26</v>
+        <v>92.97</v>
       </c>
     </row>
     <row r="29">
@@ -1087,13 +1087,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>13102</v>
+        <v>13108</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>86.78</v>
+        <v>92.14</v>
       </c>
     </row>
     <row r="30">
@@ -1110,7 +1110,7 @@
         <v>2018</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>85.85</v>
+        <v>91.86</v>
       </c>
     </row>
     <row r="31">
@@ -1127,7 +1127,7 @@
         <v>2018</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>82.62</v>
+        <v>88.62</v>
       </c>
     </row>
     <row r="32">
@@ -1144,7 +1144,7 @@
         <v>2018</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>82.07</v>
+        <v>87.91</v>
       </c>
     </row>
     <row r="33">
@@ -1161,7 +1161,7 @@
         <v>2018</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>76.4</v>
+        <v>82.09</v>
       </c>
     </row>
     <row r="34">
@@ -1178,7 +1178,7 @@
         <v>2018</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>74.44</v>
+        <v>80.03</v>
       </c>
     </row>
     <row r="35">
@@ -1195,7 +1195,7 @@
         <v>2018</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>72.42</v>
+        <v>77.69</v>
       </c>
     </row>
     <row r="36">
@@ -1212,7 +1212,7 @@
         <v>2018</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>72.33</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="37">
@@ -1229,7 +1229,7 @@
         <v>2018</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>70.93</v>
+        <v>75.99</v>
       </c>
     </row>
     <row r="38">
@@ -1246,7 +1246,7 @@
         <v>2018</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>70.66</v>
+        <v>75.52</v>
       </c>
     </row>
     <row r="39">
@@ -1263,7 +1263,7 @@
         <v>2018</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>70.63</v>
+        <v>75.02</v>
       </c>
     </row>
     <row r="40">
@@ -1280,7 +1280,7 @@
         <v>2018</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>67.93</v>
+        <v>72.81</v>
       </c>
     </row>
     <row r="41">
@@ -1297,7 +1297,7 @@
         <v>2018</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>67.35</v>
+        <v>71.78</v>
       </c>
     </row>
     <row r="42">
@@ -1314,7 +1314,7 @@
         <v>2018</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>66.27</v>
+        <v>71.09</v>
       </c>
     </row>
     <row r="43">
@@ -1331,7 +1331,7 @@
         <v>2018</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>64.77</v>
+        <v>69.37</v>
       </c>
     </row>
     <row r="44">
@@ -1348,7 +1348,7 @@
         <v>2018</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>64.57</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="45">
@@ -1365,7 +1365,7 @@
         <v>2018</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>61.96</v>
+        <v>66.46</v>
       </c>
     </row>
     <row r="46">
@@ -1382,7 +1382,7 @@
         <v>2018</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>61.57</v>
+        <v>66.02</v>
       </c>
     </row>
     <row r="47">
@@ -1399,7 +1399,7 @@
         <v>2018</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>59.22</v>
+        <v>63.26</v>
       </c>
     </row>
     <row r="48">
@@ -1416,7 +1416,7 @@
         <v>2018</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>58.79</v>
+        <v>62.74</v>
       </c>
     </row>
     <row r="49">
@@ -1433,7 +1433,7 @@
         <v>2018</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>55.09</v>
+        <v>58.82</v>
       </c>
     </row>
     <row r="50">
@@ -1450,7 +1450,7 @@
         <v>2018</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>51.14</v>
+        <v>55.12</v>
       </c>
     </row>
     <row r="51">
@@ -1467,7 +1467,7 @@
         <v>2018</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>42.96</v>
+        <v>46.27</v>
       </c>
     </row>
     <row r="52">
@@ -1484,7 +1484,7 @@
         <v>2018</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>35.55</v>
+        <v>37.71</v>
       </c>
     </row>
     <row r="53">
@@ -1501,7 +1501,7 @@
         <v>2018</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>34.97</v>
+        <v>37.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:08</t>
+    <t xml:space="preserve">2026-10-02 15:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:45</t>
+    <t xml:space="preserve">2026-10-05 16:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
